--- a/СВО_Москва_меры_поддержки.xlsx
+++ b/СВО_Москва_меры_поддержки.xlsx
@@ -11,11 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Меры для детей участников СВО" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Сводная таблица" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Полный перечень мер СВО Москва'!$A$1:$M$18</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Меры для детей участников СВО'!$A$1:$I$7</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Сводная таблица'!$A$1:$E$18</definedName>
-  </definedNames>
+  <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -23,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -36,6 +32,13 @@
       <color rgb="00FFFFFF"/>
       <sz val="11"/>
     </font>
+    <font>
+      <sz val="10"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <sz val="12"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -46,8 +49,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="008B0000"/>
-        <bgColor rgb="008B0000"/>
+        <fgColor rgb="002F5496"/>
+        <bgColor rgb="002F5496"/>
       </patternFill>
     </fill>
   </fills>
@@ -74,12 +77,10 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -445,22 +446,22 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M18"/>
+  <dimension ref="A1:M47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="4" customWidth="1" min="1" max="1"/>
-    <col width="40" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
-    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="52" customWidth="1" min="2" max="2"/>
+    <col width="25" customWidth="1" min="3" max="3"/>
+    <col width="28" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="35" customWidth="1" min="6" max="6"/>
+    <col width="45" customWidth="1" min="6" max="6"/>
     <col width="35" customWidth="1" min="7" max="7"/>
     <col width="35" customWidth="1" min="8" max="8"/>
     <col width="35" customWidth="1" min="9" max="9"/>
-    <col width="22" customWidth="1" min="10" max="10"/>
-    <col width="22" customWidth="1" min="11" max="11"/>
-    <col width="20" customWidth="1" min="12" max="12"/>
-    <col width="50" customWidth="1" min="13" max="13"/>
+    <col width="18" customWidth="1" min="10" max="10"/>
+    <col width="25" customWidth="1" min="11" max="11"/>
+    <col width="22" customWidth="1" min="12" max="12"/>
+    <col width="40" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -536,17 +537,17 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Единовременная выплата при заключении контракта о прохождении военной службы (через военкомат / пункт отбора)</t>
+          <t>Единовременная денежная выплата при заключении контракта (московская)</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Граждане, заключившие контракт с Минобороны РФ для участия в СВО (через военкоматы Москвы)</t>
+          <t>Контрактники</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>1 905 000 руб. единовременно (городская + федеральная выплаты суммарно)</t>
+          <t>1 900 000 ₽</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -556,22 +557,22 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Заключение контракта на военную службу для участия в СВО; обращение в военкомат или пункт отбора Москвы</t>
+          <t>Заключение контракта о прохождении военной службы в ВС РФ сроком 1 год и более через московский пункт отбора/военкомат Москвы с 23.07.2024</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>Единый центр поддержки участников СВО (Москва), военный комиссариат по месту жительства, пункты отбора на контракт</t>
+          <t>Единый центр поддержки участников СВО (Береговой проезд, д.8, стр.2); пункт отбора на ул. Яблочкова, д.5, стр.1; онлайн на mos.ru</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>Паспорт, заявление, контракт, реквизиты счёта</t>
+          <t>Не указано в найденных источниках (необходимы: паспорт, контракт, реквизиты счёта)</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>Выплачивается после заключения контракта и убытия к месту службы</t>
+          <t>Через Единый центр поддержки или пункт отбора. Выплачивается после заключения контракта и зачисления в воинскую часть</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
@@ -581,17 +582,17 @@
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>Единовременная / при заключении контракта</t>
+          <t>Социальная</t>
         </is>
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>Региональный (Москва) + федеральный</t>
+          <t>Региональный</t>
         </is>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>Указ Мэра Москвы; Постановление Правительства Москвы; Указ Президента РФ</t>
+          <t>Указ Мэра Москвы № 58-УМ от 23.07.2024</t>
         </is>
       </c>
     </row>
@@ -601,42 +602,42 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Единовременная выплата при ранении (увечье, контузия, травма, заболевание)</t>
+          <t>Ежемесячная городская доплата за выполнение задач СВО</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Участники СВО (мобилизованные, контрактники, добровольцы), зарегистрированные в Москве</t>
+          <t>Мобилизованные, контрактники</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>До 1 000 000 руб. (в зависимости от тяжести ранения)</t>
+          <t>50 000 ₽/мес</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Единовременно</t>
+          <t>Ежемесячно</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>Ранение, полученное при выполнении задач в ходе СВО</t>
+          <t>Участие в СВО. Для мобилизованных и контрактников</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>Единый центр поддержки участников СВО (Москва), ГКУ «Соцказначейство Москвы»</t>
+          <t>Единый центр поддержки; Департамент труда и соцзащиты г.Москвы (ДТСЗН)</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>Паспорт, документы о ранении (справка военно-врачебной комиссии), заявление, реквизиты счёта</t>
+          <t>Не указано в найденных источниках</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>Обратиться в центр поддержки или соцказначейство после установления степени тяжести ранения</t>
+          <t>Автоматически (перечисляется на счёт военнослужащего)</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
@@ -646,17 +647,17 @@
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>Компенсационная / при ранении</t>
+          <t>Социальная</t>
         </is>
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>Региональный (Москва)</t>
+          <t>Региональный</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>Постановление Правительства Москвы о дополнительных мерах поддержки участников СВО</t>
+          <t>Указ Мэра Москвы № 52-УМ от 22.09.2022 (с изм.)</t>
         </is>
       </c>
     </row>
@@ -666,42 +667,42 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Ежемесячное пособие на каждого несовершеннолетнего ребёнка</t>
+          <t>Единовременная выплата при тяжёлом ранении</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Дети участников СВО (мобилизованных, контрактников, добровольцев) — граждане, зарегистрированные в Москве</t>
+          <t>Мобилизованные, контрактники, добровольцы</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Не указано в найденных источниках (ранее — до 15 000 руб./мес. на ребёнка)</t>
+          <t>1 000 000 ₽</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Ежемесячно</t>
+          <t>Единовременно</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>Участник СВО призван/заключил контракт; ребёнок — несовершеннолетний, проживает в Москве</t>
+          <t>Тяжёлое ранение (контузия, травма, увечье) при исполнении обязанностей в СВО</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>Единый центр поддержки участников СВО, отделы соцзащиты (Соцказначейство Москвы), через mos.ru</t>
+          <t>Единый центр поддержки; ДТСЗН</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>Паспорт, свидетельство о рождении ребёнка, документ, подтверждающий статус участника СВО, заявление</t>
+          <t>Не указано в найденных источниках (вероятно: справка о ранении/ВВК, документы из воинской части)</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>Подать заявление; выплата назначается на период участия в СВО</t>
+          <t>Обращение лично или через доверенное лицо в Единый центр поддержки</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -711,17 +712,17 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>Социальная / на детей</t>
+          <t>Социальная</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>Региональный (Москва)</t>
+          <t>Региональный</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>Постановление Правительства Москвы; Указы Мэра Москвы</t>
+          <t>Указ Мэра Москвы № 52-УМ от 22.09.2022 (с изм.)</t>
         </is>
       </c>
     </row>
@@ -731,62 +732,62 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Освобождение от уплаты транспортного налога</t>
+          <t>Единовременная выплата при лёгком ранении</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Участники СВО (мобилизованные, контрактники, добровольцы)</t>
+          <t>Мобилизованные, контрактники, добровольцы</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Полное освобождение (0 руб.)</t>
+          <t>500 000 ₽</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Ежегодно (на период участия в СВО + 3 года после)</t>
+          <t>Единовременно</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>На одно ТС; применяется в том числе за прошлые периоды</t>
+          <t>Лёгкое ранение при исполнении обязанностей в СВО</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>ФНС России (через ЛК налогоплательщика или МФЦ)</t>
+          <t>Единый центр поддержки; ДТСЗН</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>Заявление о льготе, удостоверение/справка об участии в СВО</t>
+          <t>Не указано в найденных источниках</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>Подать заявление через ФНС</t>
+          <t>Обращение лично или через доверенное лицо</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>Налоговая льгота (освобождение)</t>
+          <t>Денежная выплата</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>Транспортный налог</t>
+          <t>Социальная</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>Федеральный</t>
+          <t>Региональный</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>НК РФ (льгота для участников СВО)</t>
+          <t>Указ Мэра Москвы № 52-УМ от 22.09.2022 (с изм.)</t>
         </is>
       </c>
     </row>
@@ -796,62 +797,62 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Бесплатный проезд на городском и пригородном транспорте</t>
+          <t>Единовременная выплата семье в случае гибели участника СВО</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Участники СВО (мобилизованные, контрактники, добровольцы) — при наличии Карты москвича</t>
+          <t>Члены семей (супруг(а), дети, родители)</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>100% скидка (бесплатный проезд)</t>
+          <t>3 000 000 ₽</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Постоянно, безлимитно</t>
+          <t>Единовременно</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>Регистрация в Москве; оформление Карты москвича или социальной карты</t>
+          <t>Гибель/смерть участника СВО вследствие ранения, контузии, заболевания, полученных при участии в СВО</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>МФЦ, центры «Мои документы», через mos.ru</t>
+          <t>Единый центр поддержки; ДТСЗН; Военкомат г.Москвы</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>Паспорт, документ, подтверждающий статус участника СВО, заявление</t>
+          <t>Не указано в найденных источниках</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>Оформить Карту москвича; проезд — по предъявлении карты</t>
+          <t>Обращение членов семьи с заявлением</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>Натуральная льгота</t>
+          <t>Денежная выплата</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>Транспортная</t>
+          <t>Социальная</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>Региональный (Москва)</t>
+          <t>Региональный</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>Постановление Правительства Москвы; Карта москвича</t>
+          <t>Указ Мэра Москвы № 52-УМ от 22.09.2022 (с изм.)</t>
         </is>
       </c>
     </row>
@@ -861,62 +862,62 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Скидка 50% на оплату жилого помещения и взноса на капитальный ремонт</t>
+          <t>Единовременная материальная помощь членам семей мобилизованных</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Участники СВО (мобилизованные, контрактники, добровольцы) — члены семей (приравнены к ВБД)</t>
+          <t>Члены семей мобилизованных</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>50%</t>
+          <t>50 000 ₽</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>Ежемесячно</t>
+          <t>Единовременно (была выплачена)</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>Приравнивание к ветеранам боевых действий после возвращения; для членов семьи — на период участия</t>
+          <t>Члены семей мобилизованных граждан г.Москвы</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>МФЦ, mos.ru, ГКУ «ГЦЖС» (Городской центр жилищных субсидий)</t>
+          <t>ДТСЗН</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>Паспорт, документ, подтверждающий статус, справка о составе семьи, документы на жильё</t>
+          <t>Не указано в найденных источниках</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>Обратиться в МФЦ или через mos.ru</t>
+          <t>Через органы соцзащиты</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>Скидка / компенсация</t>
+          <t>Денежная выплата</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>Жилищно-коммунальная</t>
+          <t>Социальная</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>Федеральный + региональный</t>
+          <t>Региональный</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>ФЗ №5-ФЗ «О ветеранах»; ПП Москвы №850-ПП от 07.12.2004</t>
+          <t>Указ Мэра Москвы (конкретный номер не указан в найденных источниках)</t>
         </is>
       </c>
     </row>
@@ -926,62 +927,62 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Компенсация расходов на подключение к газовым сетям</t>
+          <t>Компенсация 50% на содержание жилья, наём и взнос на капремонт (ЖКХ)</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Участники СВО (мобилизованные, контрактники, добровольцы) и члены их семей (п.1.2.10-1.2.12 ПП №2202-ПП)</t>
+          <t>Мобилизованные, контрактники, добровольцы (при статусе УБД), члены семей</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>До 198 000 руб. (до 84 000 руб. — работы, до 114 000 руб. — оборудование)</t>
+          <t>50% от расходов на содержание жилья, найма и взноса на капремонт</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Единовременно (один раз, на один дом)</t>
+          <t>Ежемесячно</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>Дом в Москве, частная собственность, регистрация в доме, работы завершены не ранее 30.09.2022, обращение не позднее 36 мес.</t>
+          <t>Наличие удостоверения ветерана боевых действий (УБД); участникам СВО и членам их семей</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>ГКУ «Социальное казначейство Москвы» (клиентские офисы)</t>
+          <t>Единый центр поддержки (Береговой проезд, д.8, стр.2); онлайн на mos.ru; Городской центр жилищных субсидий (ул. Донская, д.7, стр.1)</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>Паспорт, документ о статусе участника СВО, договор о подключении, документы о расходах, акты</t>
+          <t>Необходимо удостоверение УБД, паспорт, документы на жильё</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>Подать заявление лично в клиентский офис</t>
+          <t>Заявительный порядок. Если начисление через МФЦ — онлайн на mos.ru. Если через УК — через Городской центр жилищных субсидий</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>Компенсационная выплата</t>
+          <t>Натуральная льгота (компенсация)</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>Газификация / ЖКХ</t>
+          <t>ЖКХ</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>Региональный (Москва)</t>
+          <t>Региональный</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>Постановление Правительства Москвы от 14.11.2023 №2202-ПП (п.1.2.10-1.2.12)</t>
+          <t>ППМ (номер не указан в найденных источниках; mos.ru/news/item/143231073/)</t>
         </is>
       </c>
     </row>
@@ -991,62 +992,62 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Бесплатное горячее питание в школах</t>
+          <t>Субсидия на оплату ЖКУ (упрощённый порядок)</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Дети участников СВО (мобилизованных, контрактников, добровольцев), обучающиеся в школах Москвы</t>
+          <t>Семьи участников СВО</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>Бесплатное двухразовое горячее питание (завтрак + обед) / бесплатный обед</t>
+          <t>Размер субсидии (если доля расходов &gt;10% совокупного дохода)</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>Ежедневно (учебные дни)</t>
+          <t>Ежемесячно/периодически</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>Ребёнок учится в государственной школе Москвы; отец/мать участвует в СВО</t>
+          <t>Расходы на ЖКУ превышают 10% совокупного дохода семьи. Доходы военнослужащего и задолженность по квартплате НЕ учитываются</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>Школа (директор, классный руководитель), через mos.ru</t>
+          <t>Городской центр жилищных субсидий (ул. Донская, д.7, стр.1); Единый центр поддержки; mos.ru</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>Заявление, свидетельство о рождении, документ, подтверждающий статус участника СВО</t>
+          <t>Заявление, документы о доходах членов семьи (без учёта доходов военнослужащего)</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>Обратиться к классному руководителю или директору школы</t>
+          <t>Заявительный порядок, упрощённый порядок</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>Натуральная льгота</t>
+          <t>Натуральная льгота (субсидия)</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>Социальная / образование</t>
+          <t>ЖКХ</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>Региональный (Москва)</t>
+          <t>Региональный</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>Постановление Правительства Москвы; Указы Мэра Москвы</t>
+          <t>ППМ (конкретный номер не указан)</t>
         </is>
       </c>
     </row>
@@ -1056,62 +1057,62 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Внеочередное зачисление в дошкольные образовательные учреждения (детские сады)</t>
+          <t>Бесплатный проезд на городском транспорте Москвы (для УБД)</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Дети участников СВО (мобилизованных, контрактников, добровольцев)</t>
+          <t>Участники СВО со статусом ветерана боевых действий (УБД)</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Вне очереди (первоочередное / внеочередное зачисление)</t>
+          <t>Бесплатный проезд</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Однократно (при зачислении)</t>
+          <t>Постоянно</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>Ребёнок стоит на учёте для получения места в детском саду; родитель — участник СВО</t>
+          <t>Наличие статуса ветерана боевых действий (УБД). С 21.04.2025</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>Департамент образования г. Москвы, через mos.ru</t>
+          <t>МФЦ/соцзащита для оформления статуса; социальная карта москвича</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>Заявление, свидетельство о рождении, документ о статусе участника СВО</t>
+          <t>Удостоверение УБД, паспорт, заявление</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>Подать заявление через портал mos.ru или в ДО г. Москвы</t>
+          <t>Оформляется по заявлению; проезд по социальной карте</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>Право на внеочередное получение услуги</t>
+          <t>Натуральная льгота</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>Образование</t>
+          <t>Транспортная</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>Региональный (Москва)</t>
+          <t>Региональный</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>Указы Мэра Москвы; Распоряжения Правительства Москвы</t>
+          <t>Постановление Правительства Москвы от 15.04.2025 (в силе с 21.04.2025)</t>
         </is>
       </c>
     </row>
@@ -1121,62 +1122,62 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>Освобождение от родительской платы за детский сад</t>
+          <t>Освобождение от транспортного налога (Москва)</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Дети участников СВО (мобилизованных, контрактников, добровольцев), посещающие детские сады Москвы</t>
+          <t>Ветераны боевых действий (участники СВО со статусом УБД)</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>Освобождение от внесения родительской платы (100%)</t>
+          <t>Освобождение от уплаты за 1 ТС</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>Ежемесячно (на период участия родителя в СВО)</t>
+          <t>Ежегодно</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>Ребёнок посещает государственный детский сад Москвы</t>
+          <t>Статус УБД; одно ТС (не используемое в предпринимательстве)</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>Детский сад (заведующая, через бухгалтерию)</t>
+          <t>ФНС (личный кабинет, МФЦ, инспекция)</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>Заявление, свидетельство о рождении, документ об участии в СВО</t>
+          <t>Заявление о льготе, документы, подтверждающие статус УБД</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>Подать заявление заведующей детсада</t>
+          <t>Подать заявление в ФНС. Можно дистанционно через ЛК ФНС</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>Освобождение от платы</t>
+          <t>Налоговая льгота</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>Образование / социальная</t>
+          <t>Налоговая</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>Региональный (Москва)</t>
+          <t>Региональный</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>Указы Мэра Москвы; Распоряжения Правительства Москвы</t>
+          <t>Закон г.Москвы о транспортном налоге; ст.4 (льготные категории)</t>
         </is>
       </c>
     </row>
@@ -1186,62 +1187,62 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Бесплатные путёвки в детские оздоровительные лагеря</t>
+          <t>Льгота по налогу на имущество физлиц</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Дети участников СВО (мобилизованных, контрактников, добровольцев) в возрасте 7–15 лет (или 7–17)</t>
+          <t>Ветераны боевых действий (УБД), участники СВО</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Бесплатно (100% стоимости путёвки)</t>
+          <t>Освобождение от уплаты за 1 объект каждого вида</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>Ежегодно (в каникулярный период)</t>
+          <t>Ежегодно</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>Ребёнок — житель Москвы; родитель — участник СВО</t>
+          <t>Статус УБД/участника СВО; объект не используется в предпринимательской деятельности</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>Департамент труда и соцзащиты Москвы, через mos.ru</t>
+          <t>ФНС (личный кабинет, МФЦ, инспекция)</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>Заявление, свидетельство о рождении, документ об участии в СВО, паспорт родителя</t>
+          <t>Заявление о предоставлении льготы</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>Подать заявление через mos.ru (услуга «Получение путёвки в детский лагерь»)</t>
+          <t>Подать заявление в ФНС. Срок рассмотрения — до 30 дней</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>Натуральная льгота (путёвка)</t>
+          <t>Налоговая льгота</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>Оздоровление / отдых детей</t>
+          <t>Налоговая</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>Региональный (Москва)</t>
+          <t>Федеральный</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>Указы Мэра Москвы; Распоряжения Правительства Москвы</t>
+          <t>НК РФ; Закон г.Москвы № 47 от 19.10.2005</t>
         </is>
       </c>
     </row>
@@ -1251,62 +1252,62 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>Бесплатная юридическая помощь</t>
+          <t>Земельный налоговый вычет «6 соток»</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Участники СВО (мобилизованные, контрактники, добровольцы) и члены их семей</t>
+          <t>УБД, участники СВО, члены семей</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>Бесплатно (консультации, составление документов, представление в суде)</t>
+          <t>Вычет 600 м² (6 соток) из облагаемой площади</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>По мере необходимости</t>
+          <t>Ежегодно</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>Статус участника СВО / член семьи</t>
+          <t>Статус УБД/участника СВО/члена семьи</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>Единый центр поддержки участников СВО (Москва), Государственное юридическое бюро по г. Москве</t>
+          <t>ФНС (личный кабинет, МФЦ, инспекция)</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>Паспорт, документ, подтверждающий статус</t>
+          <t>Заявление о льготе</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>Обратиться в центр поддержки СВО или Госюрбюро</t>
+          <t>Подать заявление в ФНС</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>Социальная услуга</t>
+          <t>Налоговая льгота</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>Юридическая / правая поддержка</t>
+          <t>Налоговая</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>Региональный (Москва) + федеральный</t>
+          <t>Федеральный</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>ФЗ «О бесплатной юридической помощи»; Указы Мэра Москвы</t>
+          <t>НК РФ (федеральный вычет для льготных категорий)</t>
         </is>
       </c>
     </row>
@@ -1316,62 +1317,62 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Бесплатная психологическая помощь</t>
+          <t>Бесплатная юридическая помощь</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>Мобилизованные, добровольцы, контрактники, члены семей</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>Бесплатно</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>По мере необходимости</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>Участники СВО и члены их семей</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>Бесплатно (консультации психолога, психотерапевта)</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>По мере необходимости</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>Статус участника СВО / член семьи</t>
-        </is>
-      </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>Единый центр поддержки участников СВО (Москва), центры социальной помощи, через mos.ru</t>
+          <t>Единый центр поддержки; Государственное юридическое бюро; МФЦ</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>Паспорт, документ о статусе</t>
+          <t>Паспорт, документы, подтверждающие статус</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>Обратиться в центр поддержки или записаться через mos.ru</t>
+          <t>Заявительный порядок; консультации устно/письменно</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>Социальная услуга</t>
+          <t>Услуга</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>Медико-психологическая</t>
+          <t>Социальная / Юридическая</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>Региональный (Москва)</t>
+          <t>Федеральный+Региональный</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>Указы Мэра Москвы</t>
+          <t>ФЗ от 21.11.2011 № 324-ФЗ; ППМ (по организации)</t>
         </is>
       </c>
     </row>
@@ -1381,62 +1382,62 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>Профессиональное обучение и переобучение (в том числе в рамках проекта «Переобучение»)</t>
+          <t>Бесплатная стоматологическая помощь участникам СВО</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>Участники СВО, вернувшиеся домой</t>
+          <t>Участники СВО</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>Бесплатно (обучение востребованным профессиям, повышение квалификации)</t>
+          <t>Бесплатно</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>Однократно / по мере необходимости</t>
+          <t>По мере необходимости</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>Завершение участия в СВО; желание пройти обучение</t>
+          <t>Статус участника СВО</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>Центры занятости населения Москвы («Моя работа»), через mos.ru</t>
+          <t>Медицинские учреждения г.Москвы (по направлению); Единый центр поддержки</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>Паспорт, документы об образовании, удостоверение участника СВО</t>
+          <t>Не указано в найденных источниках</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>Обратиться в центр занятости или подать заявку через mos.ru</t>
+          <t>По направлению от Единого центра поддержки</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>Социальная услуга / обучение</t>
+          <t>Услуга</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>Профессиональная / трудовая</t>
+          <t>Медицинская</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>Региональный (Москва) + федеральный</t>
+          <t>Региональный</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>Указы Мэра Москвы; ФЗ «О занятости»</t>
+          <t>Распоряжение/ППМ (конкретный номер не указан)</t>
         </is>
       </c>
     </row>
@@ -1446,62 +1447,62 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Приоритетное предоставление жилья по договору социального найма / улучшение жилищных условий</t>
+          <t>Ежегодная диспансеризация</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Участники СВО, признанные нуждающимися в улучшении жилищных условий</t>
+          <t>Участники СВО</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>Не указано в найденных источниках (рассматривается в приоритетном порядке)</t>
+          <t>Бесплатно</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>Единовременно / по мере предоставления</t>
+          <t>Ежегодно</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>Нуждаемость в улучшении жилищных условий; статус участника СВО</t>
+          <t>Участники СВО</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>Департамент городского имущества г. Москвы, через mos.ru</t>
+          <t>Медицинские учреждения г.Москвы; Единый центр поддержки</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>Паспорт, документы о нуждаемости, документ об участии в СВО</t>
+          <t>Не указано в найденных источниках</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>Обратиться в Департамент городского имущества</t>
+          <t>По направлению</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>Жилищная помощь</t>
+          <t>Услуга</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>Жилищная</t>
+          <t>Медицинская</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>Региональный (Москва)</t>
+          <t>Региональный</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>Указы Мэра Москвы; Закон г. Москвы</t>
+          <t>Не указан в найденных источниках</t>
         </is>
       </c>
     </row>
@@ -1511,62 +1512,62 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>Компенсация расходов на найм (поднаём) жилого помещения</t>
+          <t>Медицинская реабилитация и санаторно-курортное лечение</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>Участники СВО, не имеющие жилья в Москве и не обеспеченные служебным жильём</t>
+          <t>Участники СВО</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
+          <t>Бесплатно (по показаниям)</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>По мере необходимости</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>Участники СВО, нуждающиеся в реабилитации</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>Центры реабилитации Фонда пенсионного и соцстрахования РФ; Единый центр поддержки</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
           <t>Не указано в найденных источниках</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>Ежемесячно</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>Отсутствие жилья в Москве; несение расходов на найм</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>Департамент труда и соцзащиты Москвы, через mos.ru</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>Паспорт, договор найма, документы об участии в СВО</t>
-        </is>
-      </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>Подать заявление</t>
+          <t>По направлению через Единый центр поддержки</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>Компенсационная выплата</t>
+          <t>Услуга</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>Жилищная</t>
+          <t>Медицинская</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>Региональный (Москва)</t>
+          <t>Федеральный+Региональный</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>Указы Мэра Москвы</t>
+          <t>ФЗ № 166-ФЗ, ППМ</t>
         </is>
       </c>
     </row>
@@ -1576,67 +1577,1951 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>Компенсация расходов на погребение погибшего (умершего) участника СВО</t>
+          <t>Психолого-психиатрическая помощь</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Члены семьи погибшего участника СВО (мобилизованного, контрактника, добровольца)</t>
+          <t>Участники СВО и члены семей</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>Компенсация фактических расходов на погребение (включая изготовление и установку памятника)</t>
+          <t>Бесплатно</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
+          <t>По мере необходимости</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>Участники СВО, члены их семей</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>Единый центр поддержки; мед. учреждения</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>Не указано в найденных источниках</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>Через Единый центр поддержки</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>Услуга</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>Медицинская / Социальная</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>Региональный</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>ППМ (конкретный номер не указан)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>Освобождение от начисления пеней за ЖКУ на период службы</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>Мобилизованные, добровольцы, контрактники, члены семей</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>Освобождение от пеней</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>На период службы в СВО</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>Участники СВО и члены их семей</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>Управляющая компания; ДТСЗН</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>Не указано в найденных источниках</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>Заявительный порядок</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>Натуральная льгота</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>ЖКХ</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>Федеральный</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>ФЗ № 58-ФЗ от 14.03.2022</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>Ежемесячное пособие на ребёнка (100% ПМ ребёнка)</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>Дети участников СВО</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>100% прожиточного минимума ребёнка (≈ 16 000 ₽ в 2025-2026)</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>Ежемесячно</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>Семьи участников СВО, призванных военкоматом Москвы или через пункт отбора Москвы. Упрощённый порядок — без оценки имущества и доходов</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>ДТСЗН; Единый центр поддержки</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>Заявление, свидетельство о рождении ребёнка, документы об участии в СВО</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>Заявительный порядок (упрощённый)</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>Денежная выплата</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>Социальная / Детская</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>Региональный</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>Указ Мэра Москвы (конкретный номер не указан; mos.ru/mayor/themes/1299/11512050/)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>Единовременное пособие в связи с рождением ребёнка молодым семьям</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>Молодые семьи участников СВО</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>Не указан в найденных источниках</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
           <t>Единовременно</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>Гибель участника СВО при выполнении задач</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>Военкомат, Социальный фонд России (СФР), Единый центр поддержки СВО</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>Свидетельство о смерти, справка о гибели, документы о расходах на погребение, паспорт заявителя</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>Обратиться в военкомат или СФР</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>Компенсационная выплата</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>Ритуальная / социальная</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>Федеральный + региональный</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>ФЗ «О погребении и похоронном деле»; Указы Мэра Москвы</t>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>Молодые семьи участников СВО. Упрощённый порядок — без оценки имущества, доходов и банковских счетов</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>ДТСЗН; Единый центр поддержки</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>Не указано в найденных источниках</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>Заявительный порядок (упрощённый)</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>Денежная выплата</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>Социальная / Детская</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>Региональный</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>Закон г.Москвы (номер не указан); ППМ</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>Внеочередное зачисление в детские сады (с 1,5 лет)</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>Дети участников СВО</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>Право</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>По мере зачисления</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>Дети участников СВО (мобилизованных/контрактников/добровольцев) по достижении 1,5 лет</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>Департамент образования г.Москвы; школы/детсады; mos.ru</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>Заявление, документы о статусе участника СВО, свидетельство о рождении</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>Заявительный порядок; вне очереди</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>Право</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>Образование</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>Региональный</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>Указ Мэра Москвы (конкретный номер не указан; mos.ru/mayor/themes/1299/11512050/)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>Внеочередной перевод в другой детский сад / школу</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>Дети участников СВО</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>Право</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>По мере необходимости</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>Дети участников СВО; перевод в учебное заведение, приближённое к месту жительства семьи</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>Департамент образования г.Москвы; школы/детсады; mos.ru</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>Не указано в найденных источниках</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>Заявительный порядок</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>Право</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>Образование</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>Региональный</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>Указ Мэра Москвы (конкретный номер не указан; mos.ru/mayor/themes/1299/11512050/)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>Освобождение от платы за посещение городских и муниципальных детских садов</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>Дети участников СВО</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>Освобождение от родительской платы</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>Ежемесячно (на период посещения)</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>Дети участников СВО, посещающие городские/муниципальные детские сады Москвы</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>Департамент образования; детский сад; mos.ru</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>Не указано в найденных источниках</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>Заявительный порядок</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>Натуральная льгота</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>Образование</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>Региональный</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>Указ Мэра Москвы (конкретный номер не указан; mos.ru/mayor/themes/1299/11512050/)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>Бесплатное двухразовое горячее питание в школах (1-11 классы)</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>Дети участников СВО (школьники 1-11 классов)</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>Бесплатное двухразовое питание (завтрак + обед)</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>Учебные дни</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>Дети участников СВО, обучающиеся в школах Москвы с 1 по 11 класс</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>Школа по месту учёбы; Департамент образования; mos.ru</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>Не указано в найденных источниках</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>Заявительный порядок; подать заявление в школу</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>Натуральная льгота</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>Образование / Социальная</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>Региональный</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>Указ Мэра Москвы (конкретный номер не указан; mos.ru/mayor/themes/1299/11512050/)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>Бесплатное одноразовое горячее питание в колледжах (обед)</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>Дети участников СВО (студенты колледжей)</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>Бесплатный обед</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>Учебные дни</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>Дети участников СВО, обучающиеся в городских колледжах Москвы</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>Колледж по месту учёбы; Департамент образования</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>Не указано в найденных источниках</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>Заявительный порядок</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>Натуральная льгота</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>Образование / Социальная</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>Региональный</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>Указ Мэра Москвы (конкретный номер не указан; mos.ru/mayor/themes/1299/11512050/)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>Первоочередное зачисление в группы продлённого дня (1-6 классы) + бесплатно</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>Дети участников СВО (школьники 1-6 классов)</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>Первоочередное зачисление + освобождение от оплаты</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>Учебные дни</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>Дети участников СВО, обучающиеся в 1-6 классах московских школ</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>Школа по месту учёбы</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>Не указано в найденных источниках</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>Заявительный порядок</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>Право / Натуральная льгота</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="inlineStr">
+        <is>
+          <t>Образование</t>
+        </is>
+      </c>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>Региональный</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr">
+        <is>
+          <t>Указ Мэра Москвы (конкретный номер не указан; mos.ru/mayor/themes/1299/11512050/)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>Освобождение от оплаты кружков и секций дополнительного образования</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>Дети участников СВО</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>Бесплатное посещение кружков и секций</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>Весь период занятий</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>Дети участников СВО; кружки и секции в школах и учреждениях дополнительного образования, подведомственных органам власти Москвы и ОМСУ</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>Школа; учреждение дополнительного образования</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>Не указано в найденных источниках</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>Заявительный порядок</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>Натуральная льгота</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>Образование</t>
+        </is>
+      </c>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>Региональный</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>Указ Мэра Москвы (конкретный номер не указан; mos.ru/mayor/themes/1299/11512050/)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>Перевод детей участников СВО в школу рядом с домом</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>Дети участников СВО</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>Право (внеочередной перевод)</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>По мере обращения</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>Дети участников СВО; перевод в наиболее приближённую к месту жительства образовательную организацию</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>Школа/Департамент образования</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>Не указано в найденных источниках</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>Заявительный порядок; в день обращения</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>Право</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>Образование</t>
+        </is>
+      </c>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>Федеральный+Региональный</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>Федеральные меры (gosuslugi.ru); Указ Мэра Москвы</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>Организация отдыха и оздоровления детей участников СВО</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>Дети участников СВО, находящиеся в трудной жизненной ситуации</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>Бесплатная путёвка/компенсация</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>Ежегодно (в период каникул)</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>Дети участников СВО в трудной жизненной ситуации</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>ДТСЗН; Единый центр поддержки</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>Не указано в найденных источниках</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>Заявительный порядок</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>Натуральная льгота</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t>Социальная / Детская</t>
+        </is>
+      </c>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>Региональный</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>Закон г.Москвы (номер не указан)</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>Приоритетное зачисление детей в вузы (в пределах отдельной квоты)</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>Дети участников СВО</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>Право на зачисление в пределах отдельной квоты</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>При поступлении</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>Дети участников СВО</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>ВУЗы; приёмная комиссия</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>Документы, подтверждающие статус родителя-участника СВО</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>Через приёмную комиссию вуза; зачисление в день обращения</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
+          <t>Право</t>
+        </is>
+      </c>
+      <c r="K31" s="2" t="inlineStr">
+        <is>
+          <t>Образование</t>
+        </is>
+      </c>
+      <c r="L31" s="2" t="inlineStr">
+        <is>
+          <t>Федеральный</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="inlineStr">
+        <is>
+          <t>ФЗ об образовании; Указ Президента РФ (отдельная квота)</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>Перевод детей участников СВО с платного обучения на бесплатное</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>Дети участников СВО (студенты вузов и колледжей)</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>Перевод на бюджетное место</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>По мере появления вакантных бюджетных мест</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>Отсутствие академической задолженности, дисциплинарных взысканий и задолженности по оплате</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>Образовательная организация (вуз/колледж)</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>Не указано в найденных источниках</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>Заявительный порядок через образовательную организацию</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
+          <t>Право</t>
+        </is>
+      </c>
+      <c r="K32" s="2" t="inlineStr">
+        <is>
+          <t>Образование</t>
+        </is>
+      </c>
+      <c r="L32" s="2" t="inlineStr">
+        <is>
+          <t>Федеральный</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr">
+        <is>
+          <t>ФЗ об образовании (с изм. о СВО)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>Постановка на учёт в Единый центр поддержки (филиал Фонда «Защитники Отечества»)</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>Участники СВО и члены семей</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>Услуга</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>Постоянно</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>Участники СВО и члены их семей</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>Единый центр поддержки (Береговой проезд, д.8, стр.2)</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>Паспорт, документы об участии в СВО</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>Личное обращение в Единый центр поддержки</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
+          <t>Услуга</t>
+        </is>
+      </c>
+      <c r="K33" s="2" t="inlineStr">
+        <is>
+          <t>Социальная</t>
+        </is>
+      </c>
+      <c r="L33" s="2" t="inlineStr">
+        <is>
+          <t>Региональный</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="inlineStr">
+        <is>
+          <t>ППМ</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>Социальное обслуживание на дому (пожилые родственники, инвалиды)</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>Пожилые родственники, инвалиды I-II гр., семьи с детьми-инвалидами участников СВО</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>Бесплатно</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>По мере необходимости</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>Нуждающиеся семьи участников СВО, воспитывающие детей-инвалидов; пожилые граждане; инвалиды I и II групп. Без учёта состава и доходов семьи</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>ДТСЗН; центры соцобслуживания</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>Не указано в найденных источниках</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>Заявительный порядок</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
+          <t>Услуга</t>
+        </is>
+      </c>
+      <c r="K34" s="2" t="inlineStr">
+        <is>
+          <t>Социальная</t>
+        </is>
+      </c>
+      <c r="L34" s="2" t="inlineStr">
+        <is>
+          <t>Региональный</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="inlineStr">
+        <is>
+          <t>ППМ; Закон г.Москвы № 61 от 01.10.2008</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>Первоочередное направление в дома ветеранов и стационарные учреждения</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>Пожилые родственники, инвалиды участников СВО</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>Право</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>По мере необходимости</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>Пожилые родственники участников СВО, инвалиды. Без учёта состава семьи</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>ДТСЗН</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>Не указано в найденных источниках</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>Заявительный порядок</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr">
+        <is>
+          <t>Право</t>
+        </is>
+      </c>
+      <c r="K35" s="2" t="inlineStr">
+        <is>
+          <t>Социальная</t>
+        </is>
+      </c>
+      <c r="L35" s="2" t="inlineStr">
+        <is>
+          <t>Региональный</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="inlineStr">
+        <is>
+          <t>ППМ</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>Профессиональное обучение и доп. образование (супругам и детям трудоспособного возраста)</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>Супруги и дети трудоспособного возраста участников СВО</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>Бесплатно</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>По мере организации</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>Супруги и дети (трудоспособного возраста) участников СВО</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>Центры занятости; Единый центр поддержки</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>Не указано в найденных источниках</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>Через Единый центр поддержки/центры занятости</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr">
+        <is>
+          <t>Услуга</t>
+        </is>
+      </c>
+      <c r="K36" s="2" t="inlineStr">
+        <is>
+          <t>Социальная / Образование</t>
+        </is>
+      </c>
+      <c r="L36" s="2" t="inlineStr">
+        <is>
+          <t>Региональный</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="inlineStr">
+        <is>
+          <t>ППМ</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>Содействие в трудоустройстве членов семьи</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>Члены семей участников СВО (супруги, дети трудоспособного возраста)</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>Услуга (подбор работы)</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>По мере обращения</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>Члены семей участников СВО</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>Центры занятости; Единый центр поддержки</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>Не указано в найденных источниках</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>Через Единый центр поддержки / службу занятости</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr">
+        <is>
+          <t>Услуга</t>
+        </is>
+      </c>
+      <c r="K37" s="2" t="inlineStr">
+        <is>
+          <t>Социальная / Трудоустройство</t>
+        </is>
+      </c>
+      <c r="L37" s="2" t="inlineStr">
+        <is>
+          <t>Региональный</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="inlineStr">
+        <is>
+          <t>ППМ</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>Психологическая помощь членам семей</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>Члены семей участников СВО</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>Бесплатно</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>По мере необходимости</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>Все члены семьи участника СВО</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>Единый центр поддержки; медучреждения</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>Не указано в найденных источниках</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>Через Единый центр поддержки</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr">
+        <is>
+          <t>Услуга</t>
+        </is>
+      </c>
+      <c r="K38" s="2" t="inlineStr">
+        <is>
+          <t>Социальная / Медицинская</t>
+        </is>
+      </c>
+      <c r="L38" s="2" t="inlineStr">
+        <is>
+          <t>Региональный</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="inlineStr">
+        <is>
+          <t>ППМ</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>Содействие в оформлении социальных выплат и льгот</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>Члены семей участников СВО</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>Услуга</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>По мере обращения</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>Члены семьи участника СВО</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>Единый центр поддержки</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>Не указано в найденных источниках</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>Через Единый центр поддержки</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="inlineStr">
+        <is>
+          <t>Услуга</t>
+        </is>
+      </c>
+      <c r="K39" s="2" t="inlineStr">
+        <is>
+          <t>Социальная</t>
+        </is>
+      </c>
+      <c r="L39" s="2" t="inlineStr">
+        <is>
+          <t>Региональный</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="inlineStr">
+        <is>
+          <t>ППМ</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>Освобождение от НДФЛ безвозмездно полученных доходов от СВО</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>Мобилизованные, контрактники, добровольцы</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>Освобождение от НДФЛ</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>На период участия в СВО</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>Доходы, полученные в связи с участием в СВО (денежное довольствие, выплаты, подарки от работодателей и пр.)</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>ФНС (уведомление); автоматически</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>Не указано в найденных источниках</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>Автоматически или через заявление в ФНС</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr">
+        <is>
+          <t>Налоговая льгота</t>
+        </is>
+      </c>
+      <c r="K40" s="2" t="inlineStr">
+        <is>
+          <t>Налоговая</t>
+        </is>
+      </c>
+      <c r="L40" s="2" t="inlineStr">
+        <is>
+          <t>Федеральный</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="inlineStr">
+        <is>
+          <t>НК РФ (ст. 217)</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>Стандартный налоговый вычет по НДФЛ для участников боевых действий</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>Участники СВО (при статусе УБД)</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>3000 ₽ в месяц</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>Ежемесячно</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>Статус УБД/участника боевых действий</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>ФНС; работодатель</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>Заявление, удостоверение УБД</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>Через работодателя или ФНС</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr">
+        <is>
+          <t>Налоговая льгота</t>
+        </is>
+      </c>
+      <c r="K41" s="2" t="inlineStr">
+        <is>
+          <t>Налоговая</t>
+        </is>
+      </c>
+      <c r="L41" s="2" t="inlineStr">
+        <is>
+          <t>Федеральный</t>
+        </is>
+      </c>
+      <c r="M41" s="2" t="inlineStr">
+        <is>
+          <t>НК РФ (ст. 218)</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>Кредитные каникулы для участников СВО</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>Мобилизованные, контрактники, добровольцы и члены семей</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>Отсрочка платежей на срок службы + 180 дней</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>Единовременно (на период СВО + 180 дней)</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>Участники СВО и члены семей. Каникулы — до 31.12.2025</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>Банк (кредитная организация)</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>Заявление, документы об участии в СВО</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>Подать требование банку</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr">
+        <is>
+          <t>Право</t>
+        </is>
+      </c>
+      <c r="K42" s="2" t="inlineStr">
+        <is>
+          <t>Финансовая</t>
+        </is>
+      </c>
+      <c r="L42" s="2" t="inlineStr">
+        <is>
+          <t>Федеральный</t>
+        </is>
+      </c>
+      <c r="M42" s="2" t="inlineStr">
+        <is>
+          <t>ФЗ № 377-ФЗ от 07.10.2022</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="n">
+        <v>42</v>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>Списание просроченных кредитов до 10 млн ₽ для контрактников (с 01.12.2024)</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>Контрактники (заключившие контракт с Минобороны с 01.12.2024 на ≥1 год)</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>До 10 000 000 ₽</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>Единовременно</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>Контракт с Минобороны с 01.12.2024 на срок не менее 1 года. Кредит должен быть просрочен, по нему — решение суда и открыто ИП. Не распространяется на курсантов</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>Банк/МФЦ; через процедуру банкротства</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>Не указано в найденных источниках</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>Через процедуру внесудебного банкротства или напрямую</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="inlineStr">
+        <is>
+          <t>Право</t>
+        </is>
+      </c>
+      <c r="K43" s="2" t="inlineStr">
+        <is>
+          <t>Финансовая</t>
+        </is>
+      </c>
+      <c r="L43" s="2" t="inlineStr">
+        <is>
+          <t>Федеральный</t>
+        </is>
+      </c>
+      <c r="M43" s="2" t="inlineStr">
+        <is>
+          <t>ФЗ (принят ГД 19.11.2024)</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="n">
+        <v>43</v>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>Федеральная единовременная выплата при заключении контракта</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>Контрактники</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>400 000 ₽</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>Единовременно</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>Заключение контракта о прохождении военной службы в ВС РФ</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>Пункт отбора; Минобороны</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>Не указано в найденных источниках</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>Автоматически после зачисления в часть</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="inlineStr">
+        <is>
+          <t>Денежная выплата</t>
+        </is>
+      </c>
+      <c r="K44" s="2" t="inlineStr">
+        <is>
+          <t>Социальная</t>
+        </is>
+      </c>
+      <c r="L44" s="2" t="inlineStr">
+        <is>
+          <t>Федеральный</t>
+        </is>
+      </c>
+      <c r="M44" s="2" t="inlineStr">
+        <is>
+          <t>Указ Президента РФ (отдельный акт)</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="n">
+        <v>44</v>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>Ежемесячная социальная выплата контрактникам (федеральная)</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>Контрактники (не мобилизованные)</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>15 000 ₽/мес</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>Ежемесячно</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>Контрактники (исключая мобилизованных) в течение всей СВО</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>Минобороны; автоматически</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>Не указано в найденных источниках</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>Автоматически</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="inlineStr">
+        <is>
+          <t>Денежная выплата</t>
+        </is>
+      </c>
+      <c r="K45" s="2" t="inlineStr">
+        <is>
+          <t>Социальная</t>
+        </is>
+      </c>
+      <c r="L45" s="2" t="inlineStr">
+        <is>
+          <t>Федеральный</t>
+        </is>
+      </c>
+      <c r="M45" s="2" t="inlineStr">
+        <is>
+          <t>Указ/ФЗ (конкретный номер не указан)</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="n">
+        <v>45</v>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>Ежемесячная денежная выплата (ЕДВ) ветеранам боевых действий</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>Ветераны боевых действий (УБД)</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>~3 896 ₽ (с учётом НСУ) / ~4 933 ₽ (без НСУ), актуальный размер уточняется</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>Ежемесячно</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>Статус УБД (полученный за участие в СВО)</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>СФР (Социальный фонд России)</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>Заявление, удостоверение УБД</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>Подать заявление в СФР</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr">
+        <is>
+          <t>Денежная выплата</t>
+        </is>
+      </c>
+      <c r="K46" s="2" t="inlineStr">
+        <is>
+          <t>Социальная</t>
+        </is>
+      </c>
+      <c r="L46" s="2" t="inlineStr">
+        <is>
+          <t>Федеральный</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="inlineStr">
+        <is>
+          <t>ФЗ № 5-ФЗ «О ветеранах»</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>Предоставление мер соцподдержки по оплате жилья, ЖКУ и услуг связи</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>Участники СВО и члены семей</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>Не указано в найденных источниках</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>Ежемесячно</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>Для участников СВО и членов семей</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>ДТСЗН; Единый центр поддержки</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>Не указано в найденных источниках</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>Заявительный порядок</t>
+        </is>
+      </c>
+      <c r="J47" s="2" t="inlineStr">
+        <is>
+          <t>Натуральная льгота</t>
+        </is>
+      </c>
+      <c r="K47" s="2" t="inlineStr">
+        <is>
+          <t>ЖКХ</t>
+        </is>
+      </c>
+      <c r="L47" s="2" t="inlineStr">
+        <is>
+          <t>Региональный</t>
+        </is>
+      </c>
+      <c r="M47" s="2" t="inlineStr">
+        <is>
+          <t>ППМ</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M18"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1647,18 +3532,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I7"/>
+  <dimension ref="A1:N11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="4" customWidth="1" min="1" max="1"/>
-    <col width="35" customWidth="1" min="2" max="2"/>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="55" customWidth="1" min="2" max="2"/>
     <col width="30" customWidth="1" min="3" max="3"/>
     <col width="30" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
-    <col width="20" customWidth="1" min="6" max="6"/>
-    <col width="35" customWidth="1" min="7" max="7"/>
-    <col width="30" customWidth="1" min="8" max="8"/>
+    <col width="28" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="45" customWidth="1" min="7" max="7"/>
+    <col width="35" customWidth="1" min="8" max="8"/>
     <col width="35" customWidth="1" min="9" max="9"/>
+    <col width="35" customWidth="1" min="10" max="10"/>
+    <col width="18" customWidth="1" min="11" max="11"/>
+    <col width="25" customWidth="1" min="12" max="12"/>
+    <col width="22" customWidth="1" min="13" max="13"/>
+    <col width="40" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1694,7 +3584,7 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Условия</t>
+          <t>Условия предоставления</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
@@ -1704,7 +3594,32 @@
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>Нормативный акт</t>
+          <t>Список документов</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Как получить</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Тип меры</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Категория льготы</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Уровень</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Нормативный акт-основание</t>
         </is>
       </c>
     </row>
@@ -1714,22 +3629,22 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Ежемесячное пособие на ребёнка</t>
+          <t>Ежемесячное пособие на ребёнка (100% ПМ ребёнка)</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Мобилизованный / контрактник / доброволец</t>
+          <t>Дети участников СВО</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Несовершеннолетние дети</t>
+          <t>Дети участников СВО</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Не указано в найденных источниках</t>
+          <t>100% прожиточного минимума ребёнка (≈ 16 000 ₽ в 2025-2026)</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1739,17 +3654,42 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>Участие родителя в СВО; ребёнок проживает в Москве</t>
+          <t>Семьи участников СВО, призванных военкоматом Москвы или через пункт отбора Москвы. Упрощённый порядок — без оценки имущества и доходов</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>Центр поддержки СВО, Соцказначейство</t>
+          <t>ДТСЗН; Единый центр поддержки</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>Указы Мэра Москвы</t>
+          <t>Заявление, свидетельство о рождении ребёнка, документы об участии в СВО</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>Заявительный порядок (упрощённый)</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>Денежная выплата</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>Социальная / Детская</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>Региональный</t>
+        </is>
+      </c>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
+          <t>Указ Мэра Москвы (конкретный номер не указан; mos.ru/mayor/themes/1299/11512050/)</t>
         </is>
       </c>
     </row>
@@ -1759,42 +3699,67 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Бесплатное питание в школе</t>
+          <t>Единовременное пособие в связи с рождением ребёнка молодым семьям</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Мобилизованный / контрактник / доброволец</t>
+          <t>Молодые семьи участников СВО</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Дети, обучающиеся в школах Москвы</t>
+          <t>Дети участников СВО</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Бесплатно (завтрак + обед)</t>
+          <t>Не указан в найденных источниках</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>Ежедневно (учебные дни)</t>
+          <t>Единовременно</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>Обучение в государственной школе Москвы</t>
+          <t>Молодые семьи участников СВО. Упрощённый порядок — без оценки имущества, доходов и банковских счетов</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>Школа (через директора)</t>
+          <t>ДТСЗН; Единый центр поддержки</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>Указы Мэра Москвы</t>
+          <t>Не указано в найденных источниках</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>Заявительный порядок (упрощённый)</t>
+        </is>
+      </c>
+      <c r="K3" s="2" t="inlineStr">
+        <is>
+          <t>Денежная выплата</t>
+        </is>
+      </c>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>Социальная / Детская</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>Региональный</t>
+        </is>
+      </c>
+      <c r="N3" s="2" t="inlineStr">
+        <is>
+          <t>Закон г.Москвы (номер не указан); ППМ</t>
         </is>
       </c>
     </row>
@@ -1804,12 +3769,12 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Внеочередное зачисление в детский сад</t>
+          <t>Внеочередное зачисление в детские сады (с 1,5 лет)</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Мобилизованный / контрактник / доброволец</t>
+          <t>Дети участников СВО</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -1819,27 +3784,52 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Вне очереди</t>
+          <t>Право</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>Однократно</t>
+          <t>По мере зачисления</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>Постановка на учёт для получения места</t>
+          <t>Дети участников СВО (мобилизованных/контрактников/добровольцев) по достижении 1,5 лет</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>Департамент образования, mos.ru</t>
+          <t>Департамент образования г.Москвы; школы/детсады; mos.ru</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>Указы Мэра Москвы</t>
+          <t>Заявление, документы о статусе участника СВО, свидетельство о рождении</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>Заявительный порядок; вне очереди</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>Право</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>Образование</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>Региональный</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>Указ Мэра Москвы (конкретный номер не указан; mos.ru/mayor/themes/1299/11512050/)</t>
         </is>
       </c>
     </row>
@@ -1849,42 +3839,67 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Освобождение от родительской платы за детсад</t>
+          <t>Внеочередной перевод в другой детский сад / школу</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Мобилизованный / контрактник / доброволец</t>
+          <t>Дети участников СВО</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Дети, посещающие детский сад</t>
+          <t>Дети дошкольного возраста</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Освобождение 100%</t>
+          <t>Право</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>Ежемесячно (на период участия в СВО)</t>
+          <t>По мере необходимости</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>Посещение гос. детсада Москвы</t>
+          <t>Дети участников СВО; перевод в учебное заведение, приближённое к месту жительства семьи</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>Заведующая детского сада</t>
+          <t>Департамент образования г.Москвы; школы/детсады; mos.ru</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>Указы Мэра Москвы</t>
+          <t>Не указано в найденных источниках</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>Заявительный порядок</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>Право</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>Образование</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>Региональный</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>Указ Мэра Москвы (конкретный номер не указан; mos.ru/mayor/themes/1299/11512050/)</t>
         </is>
       </c>
     </row>
@@ -1894,42 +3909,67 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Бесплатные путёвки в летние лагеря</t>
+          <t>Освобождение от платы за посещение городских и муниципальных детских садов</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Мобилизованный / контрактник / доброволец</t>
+          <t>Дети участников СВО</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Дети 7–15 (17) лет</t>
+          <t>Дети дошкольного возраста</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Бесплатно</t>
+          <t>Освобождение от родительской платы</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>Ежегодно (каникулы)</t>
+          <t>Ежемесячно (на период посещения)</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>Ребёнок — житель Москвы</t>
+          <t>Дети участников СВО, посещающие городские/муниципальные детские сады Москвы</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>Через mos.ru</t>
+          <t>Департамент образования; детский сад; mos.ru</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>Указы Мэра Москвы</t>
+          <t>Не указано в найденных источниках</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>Заявительный порядок</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>Натуральная льгота</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>Образование</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>Региональный</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>Указ Мэра Москвы (конкретный номер не указан; mos.ru/mayor/themes/1299/11512050/)</t>
         </is>
       </c>
     </row>
@@ -1939,47 +3979,351 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Компенсация за подключение газа (2202-ПП)</t>
+          <t>Бесплатное двухразовое горячее питание в школах (1-11 классы)</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Мобилизованный / контрактник / доброволец</t>
+          <t>Дети участников СВО (школьники 1-11 классов)</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Члены семьи (родители, супруги, дети)</t>
+          <t>Дети участников СВО</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>До 198 000 руб.</t>
+          <t>Бесплатное двухразовое питание (завтрак + обед)</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>Единовременно</t>
+          <t>Учебные дни</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>Дом в Москве, частная собственность</t>
+          <t>Дети участников СВО, обучающиеся в школах Москвы с 1 по 11 класс</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>ГКУ «Соцказначейство Москвы»</t>
+          <t>Школа по месту учёбы; Департамент образования; mos.ru</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>ПП Москвы №2202-ПП</t>
+          <t>Не указано в найденных источниках</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>Заявительный порядок; подать заявление в школу</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>Натуральная льгота</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>Образование / Социальная</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>Региональный</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>Указ Мэра Москвы (конкретный номер не указан; mos.ru/mayor/themes/1299/11512050/)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>Бесплатное одноразовое горячее питание в колледжах (обед)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>Дети участников СВО (студенты колледжей)</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>Студенты колледжей</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>Бесплатный обед</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>Учебные дни</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>Дети участников СВО, обучающиеся в городских колледжах Москвы</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>Колледж по месту учёбы; Департамент образования</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>Не указано в найденных источниках</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>Заявительный порядок</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>Натуральная льгота</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>Образование / Социальная</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>Региональный</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>Указ Мэра Москвы (конкретный номер не указан; mos.ru/mayor/themes/1299/11512050/)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>Первоочередное зачисление в группы продлённого дня (1-6 классы) + бесплатно</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>Дети участников СВО (школьники 1-6 классов)</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>Дети участников СВО</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>Первоочередное зачисление + освобождение от оплаты</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>Учебные дни</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>Дети участников СВО, обучающиеся в 1-6 классах московских школ</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>Школа по месту учёбы</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>Не указано в найденных источниках</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>Заявительный порядок</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>Право / Натуральная льгота</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>Образование</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>Региональный</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>Указ Мэра Москвы (конкретный номер не указан; mos.ru/mayor/themes/1299/11512050/)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>Перевод детей участников СВО в школу рядом с домом</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>Дети участников СВО</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>Дети участников СВО</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>Право (внеочередной перевод)</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>По мере обращения</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>Дети участников СВО; перевод в наиболее приближённую к месту жительства образовательную организацию</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>Школа/Департамент образования</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>Не указано в найденных источниках</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>Заявительный порядок; в день обращения</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>Право</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>Образование</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>Федеральный+Региональный</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>Федеральные меры (gosuslugi.ru); Указ Мэра Москвы</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>Перевод детей участников СВО с платного обучения на бесплатное</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>Дети участников СВО (студенты вузов и колледжей)</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>Дети участников СВО</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>Перевод на бюджетное место</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>По мере появления вакантных бюджетных мест</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>Отсутствие академической задолженности, дисциплинарных взысканий и задолженности по оплате</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>Образовательная организация (вуз/колледж)</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>Не указано в найденных источниках</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>Заявительный порядок через образовательную организацию</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>Право</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>Образование</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>Федеральный</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>ФЗ об образовании (с изм. о СВО)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I7"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1990,38 +4334,38 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E18"/>
+  <dimension ref="A1:E56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="4" customWidth="1" min="1" max="1"/>
-    <col width="40" customWidth="1" min="2" max="2"/>
-    <col width="25" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="60" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="3" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>№</t>
         </is>
       </c>
-      <c r="B1" s="3" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Мера</t>
         </is>
       </c>
-      <c r="C1" s="3" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Уровень</t>
         </is>
       </c>
-      <c r="D1" s="3" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Размер</t>
         </is>
       </c>
-      <c r="E1" s="3" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Периодичность</t>
         </is>
@@ -2033,17 +4377,17 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Единовременная выплата при заключении контракта</t>
+          <t>Единовременная денежная выплата при заключении контракта (московская)</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Региональный + федеральный</t>
+          <t>Региональный</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>1 905 000 руб.</t>
+          <t>1 900 000 ₽</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -2058,7 +4402,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Выплата при ранении</t>
+          <t>Ежемесячная городская доплата за выполнение задач СВО</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -2068,12 +4412,12 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>до 1 000 000 руб.</t>
+          <t>50 000 ₽/мес</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Единовременно</t>
+          <t>Ежемесячно</t>
         </is>
       </c>
     </row>
@@ -2083,7 +4427,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Ежемесячное пособие на ребёнка</t>
+          <t>Единовременная выплата при тяжёлом ранении</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -2093,12 +4437,12 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Не указано</t>
+          <t>1 000 000 ₽</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Ежемесячно</t>
+          <t>Единовременно</t>
         </is>
       </c>
     </row>
@@ -2108,22 +4452,22 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Освобождение от транспортного налога</t>
+          <t>Единовременная выплата при лёгком ранении</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Федеральный</t>
+          <t>Региональный</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>500 000 ₽</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Ежегодно</t>
+          <t>Единовременно</t>
         </is>
       </c>
     </row>
@@ -2133,7 +4477,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Бесплатный проезд</t>
+          <t>Единовременная выплата семье в случае гибели участника СВО</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -2143,12 +4487,12 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>3 000 000 ₽</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Постоянно</t>
+          <t>Единовременно</t>
         </is>
       </c>
     </row>
@@ -2158,22 +4502,22 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Скидка на ЖКХ (50%)</t>
+          <t>Единовременная материальная помощь членам семей мобилизованных</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Федеральный + Москва</t>
+          <t>Региональный</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>50%</t>
+          <t>50 000 ₽</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>Ежемесячно</t>
+          <t>Единовременно (была выплачена)</t>
         </is>
       </c>
     </row>
@@ -2183,7 +4527,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Компенсация за газификацию</t>
+          <t>Компенсация 50% на содержание жилья, наём и взнос на капремонт (ЖКХ)</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -2193,12 +4537,12 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>до 198 000 руб.</t>
+          <t>50% от расходов на содержание жилья, найма и взноса на капремонт</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Единовременно</t>
+          <t>Ежемесячно</t>
         </is>
       </c>
     </row>
@@ -2208,7 +4552,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Бесплатное питание в школах</t>
+          <t>Субсидия на оплату ЖКУ (упрощённый порядок)</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -2218,12 +4562,12 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>Бесплатно</t>
+          <t>Размер субсидии (если доля расходов &gt;10% совокупного дохода)</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>Ежедневно</t>
+          <t>Ежемесячно/периодически</t>
         </is>
       </c>
     </row>
@@ -2233,7 +4577,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Внеочередное зачисление в детсад</t>
+          <t>Бесплатный проезд на городском транспорте Москвы (для УБД)</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -2243,12 +4587,12 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Вне очереди</t>
+          <t>Бесплатный проезд</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Однократно</t>
+          <t>Постоянно</t>
         </is>
       </c>
     </row>
@@ -2258,7 +4602,7 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>Освобождение от платы за детсад</t>
+          <t>Освобождение от транспортного налога (Москва)</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -2268,12 +4612,12 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>Освобождение от уплаты за 1 ТС</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>Ежемесячно</t>
+          <t>Ежегодно</t>
         </is>
       </c>
     </row>
@@ -2283,17 +4627,17 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Путёвки в лагеря (дети)</t>
+          <t>Льгота по налогу на имущество физлиц</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Региональный</t>
+          <t>Федеральный</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Бесплатно</t>
+          <t>Освобождение от уплаты за 1 объект каждого вида</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -2308,22 +4652,22 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>Бесплатная юридическая помощь</t>
+          <t>Земельный налоговый вычет «6 соток»</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Региональный + федеральный</t>
+          <t>Федеральный</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>Бесплатно</t>
+          <t>Вычет 600 м² (6 соток) из облагаемой площади</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>По необходимости</t>
+          <t>Ежегодно</t>
         </is>
       </c>
     </row>
@@ -2333,12 +4677,12 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Психологическая помощь</t>
+          <t>Бесплатная юридическая помощь</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Региональный</t>
+          <t>Федеральный+Региональный</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -2348,7 +4692,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>По необходимости</t>
+          <t>По мере необходимости</t>
         </is>
       </c>
     </row>
@@ -2358,12 +4702,12 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>Профобучение / переобучение</t>
+          <t>Бесплатная стоматологическая помощь участникам СВО</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>Региональный + федеральный</t>
+          <t>Региональный</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -2373,7 +4717,7 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>Однократно</t>
+          <t>По мере необходимости</t>
         </is>
       </c>
     </row>
@@ -2383,7 +4727,7 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Помощь в жилищном вопросе</t>
+          <t>Ежегодная диспансеризация</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -2393,12 +4737,12 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>В приоритетном порядке</t>
+          <t>Бесплатно</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>По мере</t>
+          <t>Ежегодно</t>
         </is>
       </c>
     </row>
@@ -2408,22 +4752,22 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>Компенсация найма жилья</t>
+          <t>Медицинская реабилитация и санаторно-курортное лечение</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>Региональный</t>
+          <t>Федеральный+Региональный</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>Не указано</t>
+          <t>Бесплатно (по показаниям)</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>Ежемесячно</t>
+          <t>По мере необходимости</t>
         </is>
       </c>
     </row>
@@ -2433,27 +4777,807 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>Компенсация на погребение</t>
+          <t>Психолого-психиатрическая помощь</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Федеральный + региональный</t>
+          <t>Региональный</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>Фактические расходы</t>
+          <t>Бесплатно</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
+          <t>По мере необходимости</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>Освобождение от начисления пеней за ЖКУ на период службы</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>Федеральный</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>Освобождение от пеней</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>На период службы в СВО</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>Ежемесячное пособие на ребёнка (100% ПМ ребёнка)</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>Региональный</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>100% прожиточного минимума ребёнка (≈ 16 000 ₽ в 2025-2026)</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>Ежемесячно</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>Единовременное пособие в связи с рождением ребёнка молодым семьям</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>Региональный</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>Не указан в найденных источниках</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
           <t>Единовременно</t>
         </is>
       </c>
     </row>
+    <row r="22">
+      <c r="A22" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>Внеочередное зачисление в детские сады (с 1,5 лет)</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>Региональный</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>Право</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>По мере зачисления</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>Внеочередной перевод в другой детский сад / школу</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>Региональный</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>Право</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>По мере необходимости</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>Освобождение от платы за посещение городских и муниципальных детских садов</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>Региональный</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>Освобождение от родительской платы</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>Ежемесячно (на период посещения)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>Бесплатное двухразовое горячее питание в школах (1-11 классы)</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>Региональный</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>Бесплатное двухразовое питание (завтрак + обед)</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>Учебные дни</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>Бесплатное одноразовое горячее питание в колледжах (обед)</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>Региональный</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>Бесплатный обед</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>Учебные дни</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>Первоочередное зачисление в группы продлённого дня (1-6 классы) + бесплатно</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>Региональный</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>Первоочередное зачисление + освобождение от оплаты</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>Учебные дни</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>Освобождение от оплаты кружков и секций дополнительного образования</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>Региональный</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>Бесплатное посещение кружков и секций</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>Весь период занятий</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>Перевод детей участников СВО в школу рядом с домом</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>Федеральный+Региональный</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>Право (внеочередной перевод)</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>По мере обращения</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>Организация отдыха и оздоровления детей участников СВО</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>Региональный</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>Бесплатная путёвка/компенсация</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>Ежегодно (в период каникул)</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>Приоритетное зачисление детей в вузы (в пределах отдельной квоты)</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>Федеральный</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>Право на зачисление в пределах отдельной квоты</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>При поступлении</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>Перевод детей участников СВО с платного обучения на бесплатное</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>Федеральный</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>Перевод на бюджетное место</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>По мере появления вакантных бюджетных мест</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>Постановка на учёт в Единый центр поддержки (филиал Фонда «Защитники Отечества»)</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>Региональный</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>Услуга</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>Постоянно</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>Социальное обслуживание на дому (пожилые родственники, инвалиды)</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>Региональный</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>Бесплатно</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>По мере необходимости</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>Первоочередное направление в дома ветеранов и стационарные учреждения</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>Региональный</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>Право</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>По мере необходимости</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>Профессиональное обучение и доп. образование (супругам и детям трудоспособного возраста)</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>Региональный</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>Бесплатно</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>По мере организации</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>Содействие в трудоустройстве членов семьи</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>Региональный</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>Услуга (подбор работы)</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>По мере обращения</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>Психологическая помощь членам семей</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>Региональный</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>Бесплатно</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>По мере необходимости</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>Содействие в оформлении социальных выплат и льгот</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>Региональный</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>Услуга</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>По мере обращения</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>Освобождение от НДФЛ безвозмездно полученных доходов от СВО</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>Федеральный</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>Освобождение от НДФЛ</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>На период участия в СВО</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>Стандартный налоговый вычет по НДФЛ для участников боевых действий</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>Федеральный</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>3000 ₽ в месяц</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>Ежемесячно</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>Кредитные каникулы для участников СВО</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>Федеральный</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>Отсрочка платежей на срок службы + 180 дней</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>Единовременно (на период СВО + 180 дней)</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="n">
+        <v>42</v>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>Списание просроченных кредитов до 10 млн ₽ для контрактников (с 01.12.2024)</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>Федеральный</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>До 10 000 000 ₽</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>Единовременно</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="n">
+        <v>43</v>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>Федеральная единовременная выплата при заключении контракта</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>Федеральный</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>400 000 ₽</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>Единовременно</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="n">
+        <v>44</v>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>Ежемесячная социальная выплата контрактникам (федеральная)</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>Федеральный</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>15 000 ₽/мес</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>Ежемесячно</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="n">
+        <v>45</v>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>Ежемесячная денежная выплата (ЕДВ) ветеранам боевых действий</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>Федеральный</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>~3 896 ₽ (с учётом НСУ) / ~4 933 ₽ (без НСУ), актуальный размер уточняется</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>Ежемесячно</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>Предоставление мер соцподдержки по оплате жилья, ЖКУ и услуг связи</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>Региональный</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>Не указано в найденных источниках</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>Ежемесячно</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="3" t="inlineStr">
+        <is>
+          <t>СВОДНАЯ СТАТИСТИКА:</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Всего мер: 46</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Региональные (московские): 34</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Федеральные: 12</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Федеральные+Региональные: 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Мер для детей участников СВО: 10</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Источники: mos.ru, md.mos.ru, voenschet.ru, gogov.ru, dszn.ru, contract.mos.ru</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Дата составления: июль 2026</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E18"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>